--- a/artfynd/A 9563-2024 artfynd.xlsx
+++ b/artfynd/A 9563-2024 artfynd.xlsx
@@ -891,7 +891,7 @@
         <v>119750467</v>
       </c>
       <c r="B4" t="n">
-        <v>56514</v>
+        <v>56524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
